--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -1,26 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Projeto Regiao Flexibilidade\PyTSOFlex\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04973E3B-5C6D-4E9D-8E1D-92645B94F031}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>Iteracao</t>
   </si>
@@ -58,32 +52,26 @@
     <t>75.43</t>
   </si>
   <si>
-    <t>113.1</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 5.00</t>
   </si>
   <si>
-    <t xml:space="preserve"> 7.50</t>
-  </si>
-  <si>
-    <t>11.25</t>
-  </si>
-  <si>
-    <t>16.88</t>
-  </si>
-  <si>
-    <t>25.31</t>
-  </si>
-  <si>
-    <t>37.97</t>
+    <t>12.45</t>
+  </si>
+  <si>
+    <t>23.62</t>
+  </si>
+  <si>
+    <t>40.39</t>
+  </si>
+  <si>
+    <t>65.53</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -146,21 +134,13 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -198,7 +178,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -232,7 +212,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -267,10 +246,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -443,17 +421,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -470,7 +442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5">
       <c r="A2">
         <v>1</v>
       </c>
@@ -481,13 +453,13 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5">
       <c r="A3">
         <v>2</v>
       </c>
@@ -498,13 +470,13 @@
         <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E3" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5">
       <c r="A4">
         <v>3</v>
       </c>
@@ -515,13 +487,13 @@
         <v>9</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5">
       <c r="A5">
         <v>4</v>
       </c>
@@ -532,13 +504,13 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5">
       <c r="A6">
         <v>5</v>
       </c>
@@ -549,26 +521,9 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" t="b">
         <v>0</v>
       </c>
     </row>

--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="177">
+  <si>
+    <t>Ângulo</t>
+  </si>
   <si>
     <t>Iteracao</t>
   </si>
@@ -28,9 +31,27 @@
     <t>QL</t>
   </si>
   <si>
+    <t>Violação de Tensão</t>
+  </si>
+  <si>
+    <t>Violação de Fluxo</t>
+  </si>
+  <si>
+    <t>Violação de Geração</t>
+  </si>
+  <si>
     <t>Convergiu</t>
   </si>
   <si>
+    <t>Observação</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>45°</t>
+  </si>
+  <si>
     <t>Original</t>
   </si>
   <si>
@@ -40,31 +61,490 @@
     <t>14.90</t>
   </si>
   <si>
-    <t>22.35</t>
-  </si>
-  <si>
-    <t>33.53</t>
-  </si>
-  <si>
-    <t>50.29</t>
-  </si>
-  <si>
-    <t>75.43</t>
+    <t>26.01</t>
+  </si>
+  <si>
+    <t>37.13</t>
+  </si>
+  <si>
+    <t>37.24</t>
+  </si>
+  <si>
+    <t>37.35</t>
+  </si>
+  <si>
+    <t>37.46</t>
+  </si>
+  <si>
+    <t>37.57</t>
+  </si>
+  <si>
+    <t>37.68</t>
+  </si>
+  <si>
+    <t>37.79</t>
+  </si>
+  <si>
+    <t>37.90</t>
+  </si>
+  <si>
+    <t>38.02</t>
+  </si>
+  <si>
+    <t>38.13</t>
+  </si>
+  <si>
+    <t>38.24</t>
+  </si>
+  <si>
+    <t>38.35</t>
+  </si>
+  <si>
+    <t>38.46</t>
+  </si>
+  <si>
+    <t>38.57</t>
+  </si>
+  <si>
+    <t>38.68</t>
+  </si>
+  <si>
+    <t>38.79</t>
+  </si>
+  <si>
+    <t>38.90</t>
+  </si>
+  <si>
+    <t>39.02</t>
+  </si>
+  <si>
+    <t>39.13</t>
+  </si>
+  <si>
+    <t>50.24</t>
+  </si>
+  <si>
+    <t>50.35</t>
+  </si>
+  <si>
+    <t>50.46</t>
+  </si>
+  <si>
+    <t>50.57</t>
+  </si>
+  <si>
+    <t>50.68</t>
+  </si>
+  <si>
+    <t>50.80</t>
+  </si>
+  <si>
+    <t>50.91</t>
+  </si>
+  <si>
+    <t>51.02</t>
+  </si>
+  <si>
+    <t>51.13</t>
+  </si>
+  <si>
+    <t>51.24</t>
+  </si>
+  <si>
+    <t>51.35</t>
+  </si>
+  <si>
+    <t>51.46</t>
+  </si>
+  <si>
+    <t>51.57</t>
+  </si>
+  <si>
+    <t>51.68</t>
+  </si>
+  <si>
+    <t>51.80</t>
+  </si>
+  <si>
+    <t>51.91</t>
+  </si>
+  <si>
+    <t>52.02</t>
+  </si>
+  <si>
+    <t>52.13</t>
+  </si>
+  <si>
+    <t>52.24</t>
+  </si>
+  <si>
+    <t>52.35</t>
+  </si>
+  <si>
+    <t>52.46</t>
+  </si>
+  <si>
+    <t>52.57</t>
+  </si>
+  <si>
+    <t>52.69</t>
+  </si>
+  <si>
+    <t>52.80</t>
+  </si>
+  <si>
+    <t>52.91</t>
+  </si>
+  <si>
+    <t>53.02</t>
+  </si>
+  <si>
+    <t>53.13</t>
+  </si>
+  <si>
+    <t>53.24</t>
+  </si>
+  <si>
+    <t>53.35</t>
+  </si>
+  <si>
+    <t>53.46</t>
+  </si>
+  <si>
+    <t>53.57</t>
+  </si>
+  <si>
+    <t>53.69</t>
+  </si>
+  <si>
+    <t>53.80</t>
+  </si>
+  <si>
+    <t>53.91</t>
+  </si>
+  <si>
+    <t>54.02</t>
+  </si>
+  <si>
+    <t>54.13</t>
+  </si>
+  <si>
+    <t>54.24</t>
+  </si>
+  <si>
+    <t>54.35</t>
+  </si>
+  <si>
+    <t>54.46</t>
+  </si>
+  <si>
+    <t>54.57</t>
+  </si>
+  <si>
+    <t>54.69</t>
+  </si>
+  <si>
+    <t>54.80</t>
+  </si>
+  <si>
+    <t>54.91</t>
+  </si>
+  <si>
+    <t>55.02</t>
+  </si>
+  <si>
+    <t>55.13</t>
+  </si>
+  <si>
+    <t>55.24</t>
+  </si>
+  <si>
+    <t>55.35</t>
+  </si>
+  <si>
+    <t>55.46</t>
+  </si>
+  <si>
+    <t>55.57</t>
+  </si>
+  <si>
+    <t>55.69</t>
+  </si>
+  <si>
+    <t>55.80</t>
+  </si>
+  <si>
+    <t>55.91</t>
+  </si>
+  <si>
+    <t>56.02</t>
+  </si>
+  <si>
+    <t>56.13</t>
+  </si>
+  <si>
+    <t>56.24</t>
+  </si>
+  <si>
+    <t>56.35</t>
+  </si>
+  <si>
+    <t>56.46</t>
+  </si>
+  <si>
+    <t>56.57</t>
+  </si>
+  <si>
+    <t>56.69</t>
   </si>
   <si>
     <t xml:space="preserve"> 5.00</t>
   </si>
   <si>
-    <t>12.45</t>
-  </si>
-  <si>
-    <t>23.62</t>
-  </si>
-  <si>
-    <t>40.39</t>
-  </si>
-  <si>
-    <t>65.53</t>
+    <t>16.11</t>
+  </si>
+  <si>
+    <t>27.23</t>
+  </si>
+  <si>
+    <t>27.34</t>
+  </si>
+  <si>
+    <t>27.45</t>
+  </si>
+  <si>
+    <t>27.56</t>
+  </si>
+  <si>
+    <t>27.67</t>
+  </si>
+  <si>
+    <t>27.78</t>
+  </si>
+  <si>
+    <t>27.89</t>
+  </si>
+  <si>
+    <t>28.00</t>
+  </si>
+  <si>
+    <t>28.12</t>
+  </si>
+  <si>
+    <t>28.23</t>
+  </si>
+  <si>
+    <t>28.34</t>
+  </si>
+  <si>
+    <t>28.45</t>
+  </si>
+  <si>
+    <t>28.56</t>
+  </si>
+  <si>
+    <t>28.67</t>
+  </si>
+  <si>
+    <t>28.78</t>
+  </si>
+  <si>
+    <t>28.89</t>
+  </si>
+  <si>
+    <t>29.00</t>
+  </si>
+  <si>
+    <t>29.12</t>
+  </si>
+  <si>
+    <t>29.23</t>
+  </si>
+  <si>
+    <t>40.34</t>
+  </si>
+  <si>
+    <t>40.45</t>
+  </si>
+  <si>
+    <t>40.56</t>
+  </si>
+  <si>
+    <t>40.67</t>
+  </si>
+  <si>
+    <t>40.78</t>
+  </si>
+  <si>
+    <t>40.90</t>
+  </si>
+  <si>
+    <t>41.01</t>
+  </si>
+  <si>
+    <t>41.12</t>
+  </si>
+  <si>
+    <t>41.23</t>
+  </si>
+  <si>
+    <t>41.34</t>
+  </si>
+  <si>
+    <t>41.45</t>
+  </si>
+  <si>
+    <t>41.56</t>
+  </si>
+  <si>
+    <t>41.67</t>
+  </si>
+  <si>
+    <t>41.78</t>
+  </si>
+  <si>
+    <t>41.90</t>
+  </si>
+  <si>
+    <t>42.01</t>
+  </si>
+  <si>
+    <t>42.12</t>
+  </si>
+  <si>
+    <t>42.23</t>
+  </si>
+  <si>
+    <t>42.34</t>
+  </si>
+  <si>
+    <t>42.45</t>
+  </si>
+  <si>
+    <t>42.56</t>
+  </si>
+  <si>
+    <t>42.67</t>
+  </si>
+  <si>
+    <t>42.79</t>
+  </si>
+  <si>
+    <t>42.90</t>
+  </si>
+  <si>
+    <t>43.01</t>
+  </si>
+  <si>
+    <t>43.12</t>
+  </si>
+  <si>
+    <t>43.23</t>
+  </si>
+  <si>
+    <t>43.34</t>
+  </si>
+  <si>
+    <t>43.45</t>
+  </si>
+  <si>
+    <t>43.56</t>
+  </si>
+  <si>
+    <t>43.67</t>
+  </si>
+  <si>
+    <t>43.79</t>
+  </si>
+  <si>
+    <t>43.90</t>
+  </si>
+  <si>
+    <t>44.01</t>
+  </si>
+  <si>
+    <t>44.12</t>
+  </si>
+  <si>
+    <t>44.23</t>
+  </si>
+  <si>
+    <t>44.34</t>
+  </si>
+  <si>
+    <t>44.45</t>
+  </si>
+  <si>
+    <t>44.56</t>
+  </si>
+  <si>
+    <t>44.67</t>
+  </si>
+  <si>
+    <t>44.79</t>
+  </si>
+  <si>
+    <t>44.90</t>
+  </si>
+  <si>
+    <t>45.01</t>
+  </si>
+  <si>
+    <t>45.12</t>
+  </si>
+  <si>
+    <t>45.23</t>
+  </si>
+  <si>
+    <t>45.34</t>
+  </si>
+  <si>
+    <t>45.45</t>
+  </si>
+  <si>
+    <t>45.56</t>
+  </si>
+  <si>
+    <t>45.67</t>
+  </si>
+  <si>
+    <t>45.79</t>
+  </si>
+  <si>
+    <t>45.90</t>
+  </si>
+  <si>
+    <t>46.01</t>
+  </si>
+  <si>
+    <t>46.12</t>
+  </si>
+  <si>
+    <t>46.23</t>
+  </si>
+  <si>
+    <t>46.34</t>
+  </si>
+  <si>
+    <t>46.45</t>
+  </si>
+  <si>
+    <t>46.56</t>
+  </si>
+  <si>
+    <t>46.67</t>
+  </si>
+  <si>
+    <t>46.79</t>
+  </si>
+  <si>
+    <t>Não</t>
+  </si>
+  <si>
+    <t>Sim</t>
+  </si>
+  <si>
+    <t>Ponto da primeira divergência</t>
   </si>
 </sst>
 </file>
@@ -422,10 +902,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E6"/>
+  <dimension ref="A1:J83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -441,89 +921,2400 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
       <c r="C2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" t="s">
+        <v>174</v>
+      </c>
+      <c r="G2" t="s">
+        <v>174</v>
+      </c>
+      <c r="H2" t="s">
+        <v>174</v>
+      </c>
+      <c r="I2" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" t="s">
+        <v>174</v>
+      </c>
+      <c r="H3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I4" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5" t="s">
+        <v>174</v>
+      </c>
+      <c r="G5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H5" t="s">
+        <v>174</v>
+      </c>
+      <c r="I5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F6" t="s">
+        <v>174</v>
+      </c>
+      <c r="G6" t="s">
+        <v>174</v>
+      </c>
+      <c r="H6" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>98</v>
+      </c>
+      <c r="F7" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
         <v>7</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>99</v>
+      </c>
+      <c r="F8" t="s">
+        <v>174</v>
+      </c>
+      <c r="G8" t="s">
+        <v>174</v>
+      </c>
+      <c r="H8" t="s">
+        <v>174</v>
+      </c>
+      <c r="I8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" t="s">
+        <v>100</v>
+      </c>
+      <c r="F9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H9" t="s">
+        <v>174</v>
+      </c>
+      <c r="I9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" t="s">
+        <v>11</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" t="s">
+        <v>174</v>
+      </c>
+      <c r="G10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H10" t="s">
+        <v>174</v>
+      </c>
+      <c r="I10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>102</v>
+      </c>
+      <c r="F11" t="s">
+        <v>174</v>
+      </c>
+      <c r="G11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" t="s">
+        <v>23</v>
+      </c>
+      <c r="E12" t="s">
+        <v>103</v>
+      </c>
+      <c r="F12" t="s">
+        <v>174</v>
+      </c>
+      <c r="G12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" t="s">
+        <v>174</v>
+      </c>
+      <c r="I12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+      <c r="B13">
         <v>12</v>
       </c>
-      <c r="E2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" t="s">
+        <v>104</v>
+      </c>
+      <c r="F13" t="s">
+        <v>174</v>
+      </c>
+      <c r="G13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" t="s">
+        <v>174</v>
+      </c>
+      <c r="I13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>13</v>
+      </c>
+      <c r="C14" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" t="s">
+        <v>25</v>
+      </c>
+      <c r="E14" t="s">
+        <v>105</v>
+      </c>
+      <c r="F14" t="s">
+        <v>174</v>
+      </c>
+      <c r="G14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H14" t="s">
+        <v>174</v>
+      </c>
+      <c r="I14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" t="s">
+        <v>11</v>
+      </c>
+      <c r="B15">
         <v>14</v>
       </c>
-      <c r="E4" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C5" t="s">
-        <v>10</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="C15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" t="s">
+        <v>106</v>
+      </c>
+      <c r="F15" t="s">
+        <v>174</v>
+      </c>
+      <c r="G15" t="s">
+        <v>174</v>
+      </c>
+      <c r="H15" t="s">
+        <v>174</v>
+      </c>
+      <c r="I15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16">
         <v>15</v>
       </c>
-      <c r="E5" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="C16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" t="s">
+        <v>27</v>
+      </c>
+      <c r="E16" t="s">
+        <v>107</v>
+      </c>
+      <c r="F16" t="s">
+        <v>174</v>
+      </c>
+      <c r="G16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" t="s">
+        <v>174</v>
+      </c>
+      <c r="I16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
         <v>16</v>
       </c>
-      <c r="E6" t="b">
+      <c r="C17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" t="s">
+        <v>108</v>
+      </c>
+      <c r="F17" t="s">
+        <v>174</v>
+      </c>
+      <c r="G17" t="s">
+        <v>174</v>
+      </c>
+      <c r="H17" t="s">
+        <v>174</v>
+      </c>
+      <c r="I17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" t="s">
+        <v>29</v>
+      </c>
+      <c r="E18" t="s">
+        <v>109</v>
+      </c>
+      <c r="F18" t="s">
+        <v>174</v>
+      </c>
+      <c r="G18" t="s">
+        <v>174</v>
+      </c>
+      <c r="H18" t="s">
+        <v>174</v>
+      </c>
+      <c r="I18" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" t="s">
+        <v>30</v>
+      </c>
+      <c r="E19" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G19" t="s">
+        <v>174</v>
+      </c>
+      <c r="H19" t="s">
+        <v>174</v>
+      </c>
+      <c r="I19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>13</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>111</v>
+      </c>
+      <c r="F20" t="s">
+        <v>174</v>
+      </c>
+      <c r="G20" t="s">
+        <v>174</v>
+      </c>
+      <c r="H20" t="s">
+        <v>174</v>
+      </c>
+      <c r="I20" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>20</v>
+      </c>
+      <c r="C21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D21" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" t="s">
+        <v>112</v>
+      </c>
+      <c r="F21" t="s">
+        <v>174</v>
+      </c>
+      <c r="G21" t="s">
+        <v>174</v>
+      </c>
+      <c r="H21" t="s">
+        <v>174</v>
+      </c>
+      <c r="I21" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>21</v>
+      </c>
+      <c r="C22" t="s">
+        <v>13</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>113</v>
+      </c>
+      <c r="F22" t="s">
+        <v>174</v>
+      </c>
+      <c r="G22" t="s">
+        <v>174</v>
+      </c>
+      <c r="H22" t="s">
+        <v>174</v>
+      </c>
+      <c r="I22" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>22</v>
+      </c>
+      <c r="C23" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" t="s">
+        <v>114</v>
+      </c>
+      <c r="F23" t="s">
+        <v>175</v>
+      </c>
+      <c r="G23" t="s">
+        <v>174</v>
+      </c>
+      <c r="H23" t="s">
+        <v>174</v>
+      </c>
+      <c r="I23" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>23</v>
+      </c>
+      <c r="C24" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" t="s">
+        <v>35</v>
+      </c>
+      <c r="E24" t="s">
+        <v>115</v>
+      </c>
+      <c r="F24" t="s">
+        <v>175</v>
+      </c>
+      <c r="G24" t="s">
+        <v>174</v>
+      </c>
+      <c r="H24" t="s">
+        <v>174</v>
+      </c>
+      <c r="I24" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>13</v>
+      </c>
+      <c r="D25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E25" t="s">
+        <v>115</v>
+      </c>
+      <c r="F25" t="s">
+        <v>175</v>
+      </c>
+      <c r="G25" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" t="s">
+        <v>174</v>
+      </c>
+      <c r="I25" t="b">
+        <v>1</v>
+      </c>
+      <c r="J25" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>25</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26" t="s">
+        <v>36</v>
+      </c>
+      <c r="E26" t="s">
+        <v>116</v>
+      </c>
+      <c r="F26" t="s">
+        <v>175</v>
+      </c>
+      <c r="G26" t="s">
+        <v>174</v>
+      </c>
+      <c r="H26" t="s">
+        <v>174</v>
+      </c>
+      <c r="I26" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>26</v>
+      </c>
+      <c r="C27" t="s">
+        <v>13</v>
+      </c>
+      <c r="D27" t="s">
+        <v>37</v>
+      </c>
+      <c r="E27" t="s">
+        <v>117</v>
+      </c>
+      <c r="F27" t="s">
+        <v>175</v>
+      </c>
+      <c r="G27" t="s">
+        <v>174</v>
+      </c>
+      <c r="H27" t="s">
+        <v>174</v>
+      </c>
+      <c r="I27" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>27</v>
+      </c>
+      <c r="C28" t="s">
+        <v>13</v>
+      </c>
+      <c r="D28" t="s">
+        <v>38</v>
+      </c>
+      <c r="E28" t="s">
+        <v>118</v>
+      </c>
+      <c r="F28" t="s">
+        <v>175</v>
+      </c>
+      <c r="G28" t="s">
+        <v>174</v>
+      </c>
+      <c r="H28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I28" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>28</v>
+      </c>
+      <c r="C29" t="s">
+        <v>13</v>
+      </c>
+      <c r="D29" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" t="s">
+        <v>119</v>
+      </c>
+      <c r="F29" t="s">
+        <v>175</v>
+      </c>
+      <c r="G29" t="s">
+        <v>174</v>
+      </c>
+      <c r="H29" t="s">
+        <v>174</v>
+      </c>
+      <c r="I29" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>29</v>
+      </c>
+      <c r="C30" t="s">
+        <v>13</v>
+      </c>
+      <c r="D30" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" t="s">
+        <v>120</v>
+      </c>
+      <c r="F30" t="s">
+        <v>175</v>
+      </c>
+      <c r="G30" t="s">
+        <v>174</v>
+      </c>
+      <c r="H30" t="s">
+        <v>174</v>
+      </c>
+      <c r="I30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>30</v>
+      </c>
+      <c r="C31" t="s">
+        <v>13</v>
+      </c>
+      <c r="D31" t="s">
+        <v>41</v>
+      </c>
+      <c r="E31" t="s">
+        <v>121</v>
+      </c>
+      <c r="F31" t="s">
+        <v>175</v>
+      </c>
+      <c r="G31" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" t="s">
+        <v>174</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>31</v>
+      </c>
+      <c r="C32" t="s">
+        <v>13</v>
+      </c>
+      <c r="D32" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" t="s">
+        <v>122</v>
+      </c>
+      <c r="F32" t="s">
+        <v>175</v>
+      </c>
+      <c r="G32" t="s">
+        <v>174</v>
+      </c>
+      <c r="H32" t="s">
+        <v>174</v>
+      </c>
+      <c r="I32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>11</v>
+      </c>
+      <c r="B33">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>43</v>
+      </c>
+      <c r="E33" t="s">
+        <v>123</v>
+      </c>
+      <c r="F33" t="s">
+        <v>175</v>
+      </c>
+      <c r="G33" t="s">
+        <v>174</v>
+      </c>
+      <c r="H33" t="s">
+        <v>174</v>
+      </c>
+      <c r="I33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E34" t="s">
+        <v>124</v>
+      </c>
+      <c r="F34" t="s">
+        <v>175</v>
+      </c>
+      <c r="G34" t="s">
+        <v>174</v>
+      </c>
+      <c r="H34" t="s">
+        <v>174</v>
+      </c>
+      <c r="I34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>11</v>
+      </c>
+      <c r="B35">
+        <v>34</v>
+      </c>
+      <c r="C35" t="s">
+        <v>13</v>
+      </c>
+      <c r="D35" t="s">
+        <v>45</v>
+      </c>
+      <c r="E35" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" t="s">
+        <v>175</v>
+      </c>
+      <c r="G35" t="s">
+        <v>174</v>
+      </c>
+      <c r="H35" t="s">
+        <v>174</v>
+      </c>
+      <c r="I35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>11</v>
+      </c>
+      <c r="B36">
+        <v>35</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>46</v>
+      </c>
+      <c r="E36" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" t="s">
+        <v>175</v>
+      </c>
+      <c r="G36" t="s">
+        <v>174</v>
+      </c>
+      <c r="H36" t="s">
+        <v>174</v>
+      </c>
+      <c r="I36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37">
+        <v>36</v>
+      </c>
+      <c r="C37" t="s">
+        <v>13</v>
+      </c>
+      <c r="D37" t="s">
+        <v>47</v>
+      </c>
+      <c r="E37" t="s">
+        <v>127</v>
+      </c>
+      <c r="F37" t="s">
+        <v>175</v>
+      </c>
+      <c r="G37" t="s">
+        <v>174</v>
+      </c>
+      <c r="H37" t="s">
+        <v>174</v>
+      </c>
+      <c r="I37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>11</v>
+      </c>
+      <c r="B38">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>13</v>
+      </c>
+      <c r="D38" t="s">
+        <v>48</v>
+      </c>
+      <c r="E38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F38" t="s">
+        <v>175</v>
+      </c>
+      <c r="G38" t="s">
+        <v>174</v>
+      </c>
+      <c r="H38" t="s">
+        <v>174</v>
+      </c>
+      <c r="I38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>11</v>
+      </c>
+      <c r="B39">
+        <v>38</v>
+      </c>
+      <c r="C39" t="s">
+        <v>13</v>
+      </c>
+      <c r="D39" t="s">
+        <v>49</v>
+      </c>
+      <c r="E39" t="s">
+        <v>129</v>
+      </c>
+      <c r="F39" t="s">
+        <v>175</v>
+      </c>
+      <c r="G39" t="s">
+        <v>174</v>
+      </c>
+      <c r="H39" t="s">
+        <v>174</v>
+      </c>
+      <c r="I39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40">
+        <v>39</v>
+      </c>
+      <c r="C40" t="s">
+        <v>13</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" t="s">
+        <v>130</v>
+      </c>
+      <c r="F40" t="s">
+        <v>175</v>
+      </c>
+      <c r="G40" t="s">
+        <v>174</v>
+      </c>
+      <c r="H40" t="s">
+        <v>174</v>
+      </c>
+      <c r="I40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <v>40</v>
+      </c>
+      <c r="C41" t="s">
+        <v>13</v>
+      </c>
+      <c r="D41" t="s">
+        <v>51</v>
+      </c>
+      <c r="E41" t="s">
+        <v>131</v>
+      </c>
+      <c r="F41" t="s">
+        <v>175</v>
+      </c>
+      <c r="G41" t="s">
+        <v>174</v>
+      </c>
+      <c r="H41" t="s">
+        <v>174</v>
+      </c>
+      <c r="I41" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42">
+        <v>41</v>
+      </c>
+      <c r="C42" t="s">
+        <v>13</v>
+      </c>
+      <c r="D42" t="s">
+        <v>52</v>
+      </c>
+      <c r="E42" t="s">
+        <v>132</v>
+      </c>
+      <c r="F42" t="s">
+        <v>175</v>
+      </c>
+      <c r="G42" t="s">
+        <v>174</v>
+      </c>
+      <c r="H42" t="s">
+        <v>174</v>
+      </c>
+      <c r="I42" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>11</v>
+      </c>
+      <c r="B43">
+        <v>42</v>
+      </c>
+      <c r="C43" t="s">
+        <v>13</v>
+      </c>
+      <c r="D43" t="s">
+        <v>53</v>
+      </c>
+      <c r="E43" t="s">
+        <v>133</v>
+      </c>
+      <c r="F43" t="s">
+        <v>175</v>
+      </c>
+      <c r="G43" t="s">
+        <v>174</v>
+      </c>
+      <c r="H43" t="s">
+        <v>174</v>
+      </c>
+      <c r="I43" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s">
+        <v>13</v>
+      </c>
+      <c r="D44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" t="s">
+        <v>134</v>
+      </c>
+      <c r="F44" t="s">
+        <v>175</v>
+      </c>
+      <c r="G44" t="s">
+        <v>174</v>
+      </c>
+      <c r="H44" t="s">
+        <v>174</v>
+      </c>
+      <c r="I44" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>11</v>
+      </c>
+      <c r="B45">
+        <v>44</v>
+      </c>
+      <c r="C45" t="s">
+        <v>13</v>
+      </c>
+      <c r="D45" t="s">
+        <v>55</v>
+      </c>
+      <c r="E45" t="s">
+        <v>135</v>
+      </c>
+      <c r="F45" t="s">
+        <v>175</v>
+      </c>
+      <c r="G45" t="s">
+        <v>174</v>
+      </c>
+      <c r="H45" t="s">
+        <v>174</v>
+      </c>
+      <c r="I45" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46">
+        <v>45</v>
+      </c>
+      <c r="C46" t="s">
+        <v>13</v>
+      </c>
+      <c r="D46" t="s">
+        <v>56</v>
+      </c>
+      <c r="E46" t="s">
+        <v>136</v>
+      </c>
+      <c r="F46" t="s">
+        <v>175</v>
+      </c>
+      <c r="G46" t="s">
+        <v>174</v>
+      </c>
+      <c r="H46" t="s">
+        <v>174</v>
+      </c>
+      <c r="I46" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47">
+        <v>46</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47" t="s">
+        <v>57</v>
+      </c>
+      <c r="E47" t="s">
+        <v>137</v>
+      </c>
+      <c r="F47" t="s">
+        <v>175</v>
+      </c>
+      <c r="G47" t="s">
+        <v>174</v>
+      </c>
+      <c r="H47" t="s">
+        <v>174</v>
+      </c>
+      <c r="I47" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>11</v>
+      </c>
+      <c r="B48">
+        <v>47</v>
+      </c>
+      <c r="C48" t="s">
+        <v>13</v>
+      </c>
+      <c r="D48" t="s">
+        <v>58</v>
+      </c>
+      <c r="E48" t="s">
+        <v>138</v>
+      </c>
+      <c r="F48" t="s">
+        <v>175</v>
+      </c>
+      <c r="G48" t="s">
+        <v>174</v>
+      </c>
+      <c r="H48" t="s">
+        <v>174</v>
+      </c>
+      <c r="I48" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>11</v>
+      </c>
+      <c r="B49">
+        <v>48</v>
+      </c>
+      <c r="C49" t="s">
+        <v>13</v>
+      </c>
+      <c r="D49" t="s">
+        <v>59</v>
+      </c>
+      <c r="E49" t="s">
+        <v>139</v>
+      </c>
+      <c r="F49" t="s">
+        <v>175</v>
+      </c>
+      <c r="G49" t="s">
+        <v>174</v>
+      </c>
+      <c r="H49" t="s">
+        <v>174</v>
+      </c>
+      <c r="I49" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50">
+        <v>49</v>
+      </c>
+      <c r="C50" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" t="s">
+        <v>60</v>
+      </c>
+      <c r="E50" t="s">
+        <v>140</v>
+      </c>
+      <c r="F50" t="s">
+        <v>175</v>
+      </c>
+      <c r="G50" t="s">
+        <v>174</v>
+      </c>
+      <c r="H50" t="s">
+        <v>174</v>
+      </c>
+      <c r="I50" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51" t="s">
+        <v>11</v>
+      </c>
+      <c r="B51">
+        <v>50</v>
+      </c>
+      <c r="C51" t="s">
+        <v>13</v>
+      </c>
+      <c r="D51" t="s">
+        <v>61</v>
+      </c>
+      <c r="E51" t="s">
+        <v>141</v>
+      </c>
+      <c r="F51" t="s">
+        <v>175</v>
+      </c>
+      <c r="G51" t="s">
+        <v>174</v>
+      </c>
+      <c r="H51" t="s">
+        <v>174</v>
+      </c>
+      <c r="I51" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52">
+        <v>51</v>
+      </c>
+      <c r="C52" t="s">
+        <v>13</v>
+      </c>
+      <c r="D52" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" t="s">
+        <v>142</v>
+      </c>
+      <c r="F52" t="s">
+        <v>175</v>
+      </c>
+      <c r="G52" t="s">
+        <v>174</v>
+      </c>
+      <c r="H52" t="s">
+        <v>174</v>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9">
+      <c r="A53" t="s">
+        <v>11</v>
+      </c>
+      <c r="B53">
+        <v>52</v>
+      </c>
+      <c r="C53" t="s">
+        <v>13</v>
+      </c>
+      <c r="D53" t="s">
+        <v>63</v>
+      </c>
+      <c r="E53" t="s">
+        <v>143</v>
+      </c>
+      <c r="F53" t="s">
+        <v>175</v>
+      </c>
+      <c r="G53" t="s">
+        <v>174</v>
+      </c>
+      <c r="H53" t="s">
+        <v>174</v>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9">
+      <c r="A54" t="s">
+        <v>11</v>
+      </c>
+      <c r="B54">
+        <v>53</v>
+      </c>
+      <c r="C54" t="s">
+        <v>13</v>
+      </c>
+      <c r="D54" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" t="s">
+        <v>144</v>
+      </c>
+      <c r="F54" t="s">
+        <v>175</v>
+      </c>
+      <c r="G54" t="s">
+        <v>174</v>
+      </c>
+      <c r="H54" t="s">
+        <v>174</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9">
+      <c r="A55" t="s">
+        <v>11</v>
+      </c>
+      <c r="B55">
+        <v>54</v>
+      </c>
+      <c r="C55" t="s">
+        <v>13</v>
+      </c>
+      <c r="D55" t="s">
+        <v>65</v>
+      </c>
+      <c r="E55" t="s">
+        <v>145</v>
+      </c>
+      <c r="F55" t="s">
+        <v>175</v>
+      </c>
+      <c r="G55" t="s">
+        <v>174</v>
+      </c>
+      <c r="H55" t="s">
+        <v>174</v>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="A56" t="s">
+        <v>11</v>
+      </c>
+      <c r="B56">
+        <v>55</v>
+      </c>
+      <c r="C56" t="s">
+        <v>13</v>
+      </c>
+      <c r="D56" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" t="s">
+        <v>146</v>
+      </c>
+      <c r="F56" t="s">
+        <v>175</v>
+      </c>
+      <c r="G56" t="s">
+        <v>174</v>
+      </c>
+      <c r="H56" t="s">
+        <v>174</v>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" t="s">
+        <v>11</v>
+      </c>
+      <c r="B57">
+        <v>56</v>
+      </c>
+      <c r="C57" t="s">
+        <v>13</v>
+      </c>
+      <c r="D57" t="s">
+        <v>67</v>
+      </c>
+      <c r="E57" t="s">
+        <v>147</v>
+      </c>
+      <c r="F57" t="s">
+        <v>175</v>
+      </c>
+      <c r="G57" t="s">
+        <v>174</v>
+      </c>
+      <c r="H57" t="s">
+        <v>174</v>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58">
+        <v>57</v>
+      </c>
+      <c r="C58" t="s">
+        <v>13</v>
+      </c>
+      <c r="D58" t="s">
+        <v>68</v>
+      </c>
+      <c r="E58" t="s">
+        <v>148</v>
+      </c>
+      <c r="F58" t="s">
+        <v>175</v>
+      </c>
+      <c r="G58" t="s">
+        <v>174</v>
+      </c>
+      <c r="H58" t="s">
+        <v>174</v>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9">
+      <c r="A59" t="s">
+        <v>11</v>
+      </c>
+      <c r="B59">
+        <v>58</v>
+      </c>
+      <c r="C59" t="s">
+        <v>13</v>
+      </c>
+      <c r="D59" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" t="s">
+        <v>149</v>
+      </c>
+      <c r="F59" t="s">
+        <v>175</v>
+      </c>
+      <c r="G59" t="s">
+        <v>174</v>
+      </c>
+      <c r="H59" t="s">
+        <v>174</v>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9">
+      <c r="A60" t="s">
+        <v>11</v>
+      </c>
+      <c r="B60">
+        <v>59</v>
+      </c>
+      <c r="C60" t="s">
+        <v>13</v>
+      </c>
+      <c r="D60" t="s">
+        <v>70</v>
+      </c>
+      <c r="E60" t="s">
+        <v>150</v>
+      </c>
+      <c r="F60" t="s">
+        <v>175</v>
+      </c>
+      <c r="G60" t="s">
+        <v>174</v>
+      </c>
+      <c r="H60" t="s">
+        <v>174</v>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9">
+      <c r="A61" t="s">
+        <v>11</v>
+      </c>
+      <c r="B61">
+        <v>60</v>
+      </c>
+      <c r="C61" t="s">
+        <v>13</v>
+      </c>
+      <c r="D61" t="s">
+        <v>71</v>
+      </c>
+      <c r="E61" t="s">
+        <v>151</v>
+      </c>
+      <c r="F61" t="s">
+        <v>175</v>
+      </c>
+      <c r="G61" t="s">
+        <v>174</v>
+      </c>
+      <c r="H61" t="s">
+        <v>174</v>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62">
+        <v>61</v>
+      </c>
+      <c r="C62" t="s">
+        <v>13</v>
+      </c>
+      <c r="D62" t="s">
+        <v>72</v>
+      </c>
+      <c r="E62" t="s">
+        <v>152</v>
+      </c>
+      <c r="F62" t="s">
+        <v>175</v>
+      </c>
+      <c r="G62" t="s">
+        <v>174</v>
+      </c>
+      <c r="H62" t="s">
+        <v>174</v>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9">
+      <c r="A63" t="s">
+        <v>11</v>
+      </c>
+      <c r="B63">
+        <v>62</v>
+      </c>
+      <c r="C63" t="s">
+        <v>13</v>
+      </c>
+      <c r="D63" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" t="s">
+        <v>153</v>
+      </c>
+      <c r="F63" t="s">
+        <v>175</v>
+      </c>
+      <c r="G63" t="s">
+        <v>174</v>
+      </c>
+      <c r="H63" t="s">
+        <v>174</v>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9">
+      <c r="A64" t="s">
+        <v>11</v>
+      </c>
+      <c r="B64">
+        <v>63</v>
+      </c>
+      <c r="C64" t="s">
+        <v>13</v>
+      </c>
+      <c r="D64" t="s">
+        <v>74</v>
+      </c>
+      <c r="E64" t="s">
+        <v>154</v>
+      </c>
+      <c r="F64" t="s">
+        <v>175</v>
+      </c>
+      <c r="G64" t="s">
+        <v>174</v>
+      </c>
+      <c r="H64" t="s">
+        <v>174</v>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:9">
+      <c r="A65" t="s">
+        <v>11</v>
+      </c>
+      <c r="B65">
+        <v>64</v>
+      </c>
+      <c r="C65" t="s">
+        <v>13</v>
+      </c>
+      <c r="D65" t="s">
+        <v>75</v>
+      </c>
+      <c r="E65" t="s">
+        <v>155</v>
+      </c>
+      <c r="F65" t="s">
+        <v>175</v>
+      </c>
+      <c r="G65" t="s">
+        <v>174</v>
+      </c>
+      <c r="H65" t="s">
+        <v>174</v>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:9">
+      <c r="A66" t="s">
+        <v>11</v>
+      </c>
+      <c r="B66">
+        <v>65</v>
+      </c>
+      <c r="C66" t="s">
+        <v>13</v>
+      </c>
+      <c r="D66" t="s">
+        <v>76</v>
+      </c>
+      <c r="E66" t="s">
+        <v>156</v>
+      </c>
+      <c r="F66" t="s">
+        <v>175</v>
+      </c>
+      <c r="G66" t="s">
+        <v>174</v>
+      </c>
+      <c r="H66" t="s">
+        <v>174</v>
+      </c>
+      <c r="I66" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:9">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67">
+        <v>66</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67" t="s">
+        <v>77</v>
+      </c>
+      <c r="E67" t="s">
+        <v>157</v>
+      </c>
+      <c r="F67" t="s">
+        <v>175</v>
+      </c>
+      <c r="G67" t="s">
+        <v>174</v>
+      </c>
+      <c r="H67" t="s">
+        <v>174</v>
+      </c>
+      <c r="I67" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:9">
+      <c r="A68" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68">
+        <v>67</v>
+      </c>
+      <c r="C68" t="s">
+        <v>13</v>
+      </c>
+      <c r="D68" t="s">
+        <v>78</v>
+      </c>
+      <c r="E68" t="s">
+        <v>158</v>
+      </c>
+      <c r="F68" t="s">
+        <v>175</v>
+      </c>
+      <c r="G68" t="s">
+        <v>174</v>
+      </c>
+      <c r="H68" t="s">
+        <v>174</v>
+      </c>
+      <c r="I68" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:9">
+      <c r="A69" t="s">
+        <v>11</v>
+      </c>
+      <c r="B69">
+        <v>68</v>
+      </c>
+      <c r="C69" t="s">
+        <v>13</v>
+      </c>
+      <c r="D69" t="s">
+        <v>79</v>
+      </c>
+      <c r="E69" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" t="s">
+        <v>175</v>
+      </c>
+      <c r="G69" t="s">
+        <v>174</v>
+      </c>
+      <c r="H69" t="s">
+        <v>174</v>
+      </c>
+      <c r="I69" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:9">
+      <c r="A70" t="s">
+        <v>11</v>
+      </c>
+      <c r="B70">
+        <v>69</v>
+      </c>
+      <c r="C70" t="s">
+        <v>13</v>
+      </c>
+      <c r="D70" t="s">
+        <v>80</v>
+      </c>
+      <c r="E70" t="s">
+        <v>160</v>
+      </c>
+      <c r="F70" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" t="s">
+        <v>174</v>
+      </c>
+      <c r="H70" t="s">
+        <v>174</v>
+      </c>
+      <c r="I70" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:9">
+      <c r="A71" t="s">
+        <v>11</v>
+      </c>
+      <c r="B71">
+        <v>70</v>
+      </c>
+      <c r="C71" t="s">
+        <v>13</v>
+      </c>
+      <c r="D71" t="s">
+        <v>81</v>
+      </c>
+      <c r="E71" t="s">
+        <v>161</v>
+      </c>
+      <c r="F71" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" t="s">
+        <v>174</v>
+      </c>
+      <c r="H71" t="s">
+        <v>174</v>
+      </c>
+      <c r="I71" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:9">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72">
+        <v>71</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>82</v>
+      </c>
+      <c r="E72" t="s">
+        <v>162</v>
+      </c>
+      <c r="F72" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" t="s">
+        <v>174</v>
+      </c>
+      <c r="H72" t="s">
+        <v>174</v>
+      </c>
+      <c r="I72" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:9">
+      <c r="A73" t="s">
+        <v>11</v>
+      </c>
+      <c r="B73">
+        <v>72</v>
+      </c>
+      <c r="C73" t="s">
+        <v>13</v>
+      </c>
+      <c r="D73" t="s">
+        <v>83</v>
+      </c>
+      <c r="E73" t="s">
+        <v>163</v>
+      </c>
+      <c r="F73" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" t="s">
+        <v>174</v>
+      </c>
+      <c r="H73" t="s">
+        <v>174</v>
+      </c>
+      <c r="I73" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:9">
+      <c r="A74" t="s">
+        <v>11</v>
+      </c>
+      <c r="B74">
+        <v>73</v>
+      </c>
+      <c r="C74" t="s">
+        <v>13</v>
+      </c>
+      <c r="D74" t="s">
+        <v>84</v>
+      </c>
+      <c r="E74" t="s">
+        <v>164</v>
+      </c>
+      <c r="F74" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" t="s">
+        <v>174</v>
+      </c>
+      <c r="H74" t="s">
+        <v>174</v>
+      </c>
+      <c r="I74" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:9">
+      <c r="A75" t="s">
+        <v>11</v>
+      </c>
+      <c r="B75">
+        <v>74</v>
+      </c>
+      <c r="C75" t="s">
+        <v>13</v>
+      </c>
+      <c r="D75" t="s">
+        <v>85</v>
+      </c>
+      <c r="E75" t="s">
+        <v>165</v>
+      </c>
+      <c r="F75" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" t="s">
+        <v>174</v>
+      </c>
+      <c r="H75" t="s">
+        <v>174</v>
+      </c>
+      <c r="I75" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9">
+      <c r="A76" t="s">
+        <v>11</v>
+      </c>
+      <c r="B76">
+        <v>75</v>
+      </c>
+      <c r="C76" t="s">
+        <v>13</v>
+      </c>
+      <c r="D76" t="s">
+        <v>86</v>
+      </c>
+      <c r="E76" t="s">
+        <v>166</v>
+      </c>
+      <c r="F76" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" t="s">
+        <v>174</v>
+      </c>
+      <c r="H76" t="s">
+        <v>174</v>
+      </c>
+      <c r="I76" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9">
+      <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77">
+        <v>76</v>
+      </c>
+      <c r="C77" t="s">
+        <v>13</v>
+      </c>
+      <c r="D77" t="s">
+        <v>87</v>
+      </c>
+      <c r="E77" t="s">
+        <v>167</v>
+      </c>
+      <c r="F77" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" t="s">
+        <v>174</v>
+      </c>
+      <c r="H77" t="s">
+        <v>174</v>
+      </c>
+      <c r="I77" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9">
+      <c r="A78" t="s">
+        <v>11</v>
+      </c>
+      <c r="B78">
+        <v>77</v>
+      </c>
+      <c r="C78" t="s">
+        <v>13</v>
+      </c>
+      <c r="D78" t="s">
+        <v>88</v>
+      </c>
+      <c r="E78" t="s">
+        <v>168</v>
+      </c>
+      <c r="F78" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" t="s">
+        <v>174</v>
+      </c>
+      <c r="H78" t="s">
+        <v>174</v>
+      </c>
+      <c r="I78" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9">
+      <c r="A79" t="s">
+        <v>11</v>
+      </c>
+      <c r="B79">
+        <v>78</v>
+      </c>
+      <c r="C79" t="s">
+        <v>13</v>
+      </c>
+      <c r="D79" t="s">
+        <v>89</v>
+      </c>
+      <c r="E79" t="s">
+        <v>169</v>
+      </c>
+      <c r="F79" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" t="s">
+        <v>174</v>
+      </c>
+      <c r="H79" t="s">
+        <v>174</v>
+      </c>
+      <c r="I79" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:9">
+      <c r="A80" t="s">
+        <v>11</v>
+      </c>
+      <c r="B80">
+        <v>79</v>
+      </c>
+      <c r="C80" t="s">
+        <v>13</v>
+      </c>
+      <c r="D80" t="s">
+        <v>90</v>
+      </c>
+      <c r="E80" t="s">
+        <v>170</v>
+      </c>
+      <c r="F80" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" t="s">
+        <v>174</v>
+      </c>
+      <c r="H80" t="s">
+        <v>174</v>
+      </c>
+      <c r="I80" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="81" spans="1:9">
+      <c r="A81" t="s">
+        <v>11</v>
+      </c>
+      <c r="B81">
+        <v>80</v>
+      </c>
+      <c r="C81" t="s">
+        <v>13</v>
+      </c>
+      <c r="D81" t="s">
+        <v>91</v>
+      </c>
+      <c r="E81" t="s">
+        <v>171</v>
+      </c>
+      <c r="F81" t="s">
+        <v>175</v>
+      </c>
+      <c r="G81" t="s">
+        <v>174</v>
+      </c>
+      <c r="H81" t="s">
+        <v>174</v>
+      </c>
+      <c r="I81" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:9">
+      <c r="A82" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82">
+        <v>81</v>
+      </c>
+      <c r="C82" t="s">
+        <v>13</v>
+      </c>
+      <c r="D82" t="s">
+        <v>92</v>
+      </c>
+      <c r="E82" t="s">
+        <v>172</v>
+      </c>
+      <c r="F82" t="s">
+        <v>175</v>
+      </c>
+      <c r="G82" t="s">
+        <v>174</v>
+      </c>
+      <c r="H82" t="s">
+        <v>174</v>
+      </c>
+      <c r="I82" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:9">
+      <c r="A83" t="s">
+        <v>11</v>
+      </c>
+      <c r="B83">
+        <v>82</v>
+      </c>
+      <c r="C83" t="s">
+        <v>13</v>
+      </c>
+      <c r="D83" t="s">
+        <v>93</v>
+      </c>
+      <c r="E83" t="s">
+        <v>173</v>
+      </c>
+      <c r="F83" t="s">
+        <v>175</v>
+      </c>
+      <c r="G83" t="s">
+        <v>174</v>
+      </c>
+      <c r="H83" t="s">
+        <v>174</v>
+      </c>
+      <c r="I83" t="b">
         <v>0</v>
       </c>
     </row>
